--- a/artfynd/Blåbergssjön artfynd.xlsx
+++ b/artfynd/Blåbergssjön artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56824762</v>
+        <v>56824764</v>
       </c>
       <c r="B2" t="n">
-        <v>91210</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>686318</v>
+        <v>686384</v>
       </c>
       <c r="R2" t="n">
-        <v>7095582</v>
+        <v>7095541</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56824761</v>
+        <v>56824766</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>686217</v>
+        <v>686361</v>
       </c>
       <c r="R3" t="n">
-        <v>7095651</v>
+        <v>7095359</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>56824758</v>
+        <v>56824755</v>
       </c>
       <c r="B4" t="n">
-        <v>79066</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6450</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>686118</v>
+        <v>686146</v>
       </c>
       <c r="R4" t="n">
-        <v>7095434</v>
+        <v>7095411</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>mossigt block</t>
+          <t>gammal tallåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>56824759</v>
+        <v>56824757</v>
       </c>
       <c r="B5" t="n">
-        <v>92535</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>686070</v>
+        <v>686118</v>
       </c>
       <c r="R5" t="n">
-        <v>7095526</v>
+        <v>7095419</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,6 +1081,11 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>törvedshögstubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>56824755</v>
+        <v>56824759</v>
       </c>
       <c r="B6" t="n">
-        <v>78647</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>686146</v>
+        <v>686070</v>
       </c>
       <c r="R6" t="n">
-        <v>7095411</v>
+        <v>7095526</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,11 +1188,6 @@
       <c r="AI6" t="inlineStr">
         <is>
           <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>gammal tallåga</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>56824757</v>
+        <v>56824774</v>
       </c>
       <c r="B7" t="n">
-        <v>78647</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>686118</v>
+        <v>686316</v>
       </c>
       <c r="R7" t="n">
-        <v>7095419</v>
+        <v>7095128</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,11 +1290,6 @@
       <c r="AI7" t="inlineStr">
         <is>
           <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>törvedshögstubbe</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1312,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>56824752</v>
+        <v>126380529</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,34 +1318,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hötjärnberget, Ång</t>
+          <t>Övre Nyland, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>686154</v>
+        <v>686123</v>
       </c>
       <c r="R8" t="n">
-        <v>7095366</v>
+        <v>7095360</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,12 +1372,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1393,71 +1388,61 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Carl Jansson, Rolf Nylinder</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126380527</v>
+        <v>56824762</v>
       </c>
       <c r="B9" t="n">
-        <v>79569</v>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Övre Nyland, Ång</t>
+          <t>Hötjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>686123</v>
+        <v>686318</v>
       </c>
       <c r="R9" t="n">
-        <v>7095396</v>
+        <v>7095582</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,12 +1469,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,75 +1486,70 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Carl Jansson, Rolf Nylinder</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126380528</v>
+        <v>56824752</v>
       </c>
       <c r="B10" t="n">
-        <v>79598</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Övre Nyland, Ång</t>
+          <t>Hötjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>686122</v>
+        <v>686154</v>
       </c>
       <c r="R10" t="n">
-        <v>7095399</v>
+        <v>7095366</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,12 +1576,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1613,75 +1593,70 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
         <is>
           <t>tall</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Carl Jansson, Rolf Nylinder</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126380529</v>
+        <v>56824775</v>
       </c>
       <c r="B11" t="n">
-        <v>92535</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Övre Nyland, Ång</t>
+          <t>Hötjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>686123</v>
+        <v>686323</v>
       </c>
       <c r="R11" t="n">
-        <v>7095360</v>
+        <v>7095086</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,12 +1683,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1724,26 +1699,36 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Carl Jansson, Rolf Nylinder</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>56824756</v>
+        <v>126380526</v>
       </c>
       <c r="B12" t="n">
-        <v>79569</v>
+        <v>78730</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,34 +1736,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hötjärnberget, Ång</t>
+          <t>Övre Nyland, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>686118</v>
+        <v>686123</v>
       </c>
       <c r="R12" t="n">
-        <v>7095419</v>
+        <v>7095396</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,12 +1790,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,57 +1807,62 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>törvedshögstubbe</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Carl Jansson, Rolf Nylinder</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>56824760</v>
+        <v>56824758</v>
       </c>
       <c r="B13" t="n">
-        <v>92535</v>
+        <v>79413</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6450</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>686207</v>
+        <v>686118</v>
       </c>
       <c r="R13" t="n">
-        <v>7095652</v>
+        <v>7095434</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,6 +1922,11 @@
       <c r="AI13" t="inlineStr">
         <is>
           <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>mossigt block</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1949,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>56824765</v>
+        <v>56824763</v>
       </c>
       <c r="B14" t="n">
-        <v>5492</v>
+        <v>79413</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,21 +1955,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>101410</v>
+        <v>6450</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>686273</v>
+        <v>686385</v>
       </c>
       <c r="R14" t="n">
-        <v>7095472</v>
+        <v>7095546</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2038,7 +2033,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>gammal tall</t>
+          <t>mossigt block</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2056,45 +2051,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>56824774</v>
+        <v>126380528</v>
       </c>
       <c r="B15" t="n">
-        <v>92535</v>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hötjärnberget, Ång</t>
+          <t>Övre Nyland, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>686316</v>
+        <v>686122</v>
       </c>
       <c r="R15" t="n">
-        <v>7095128</v>
+        <v>7095399</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2121,12 +2116,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2138,30 +2133,40 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Carl Jansson, Rolf Nylinder</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126380526</v>
+        <v>56824773</v>
       </c>
       <c r="B16" t="n">
-        <v>78386</v>
+        <v>78334</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,34 +2174,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6437</v>
+        <v>6487</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Övre Nyland, Ång</t>
+          <t>Hötjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>686123</v>
+        <v>686371</v>
       </c>
       <c r="R16" t="n">
-        <v>7095396</v>
+        <v>7095205</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2223,12 +2228,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2240,40 +2245,35 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>törvedshögstubbe</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Carl Jansson, Rolf Nylinder</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>56824754</v>
+        <v>56824765</v>
       </c>
       <c r="B17" t="n">
-        <v>78739</v>
+        <v>5495</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2281,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>101410</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>686140</v>
+        <v>686273</v>
       </c>
       <c r="R17" t="n">
-        <v>7095359</v>
+        <v>7095472</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>gammal tall</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2374,6 +2374,541 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>56824754</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hötjärnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>686140</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7095359</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2015-05-18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2015-10-30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>56824756</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hötjärnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>686118</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7095419</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2015-05-18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2015-10-30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>törvedshögstubbe</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126380527</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Övre Nyland, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>686123</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7095396</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Rolf Nylinder</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>56824760</v>
+      </c>
+      <c r="B21" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hötjärnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>686207</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7095652</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2015-05-18</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2015-10-30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>56824761</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hötjärnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>686217</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7095651</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2015-05-18</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2015-10-30</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
